--- a/artfynd/A 25236-2026 artfynd.xlsx
+++ b/artfynd/A 25236-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73208920</v>
+        <v>73208936</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489254.1244601483</v>
+        <v>489226</v>
       </c>
       <c r="R2" t="n">
-        <v>6341198.131531792</v>
+        <v>6341178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73208938</v>
+        <v>73208937</v>
       </c>
       <c r="B3" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489260.1139592719</v>
+        <v>489254</v>
       </c>
       <c r="R3" t="n">
-        <v>6341206.238495814</v>
+        <v>6341198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,14 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov asplåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73208918</v>
+        <v>73208938</v>
       </c>
       <c r="B4" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489254.1244601483</v>
+        <v>489260</v>
       </c>
       <c r="R4" t="n">
-        <v>6341198.131531792</v>
+        <v>6341206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,24 +947,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov asplåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73208917</v>
+        <v>73208955</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489225.8582057045</v>
+        <v>489250</v>
       </c>
       <c r="R5" t="n">
-        <v>6341178.169614562</v>
+        <v>6341265</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,24 +1044,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov asplåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73208936</v>
+        <v>73208920</v>
       </c>
       <c r="B6" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489225.8582057045</v>
+        <v>489254</v>
       </c>
       <c r="R6" t="n">
-        <v>6341178.169614562</v>
+        <v>6341198</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1141,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1255,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73208937</v>
+        <v>73208919</v>
       </c>
       <c r="B7" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489254.1244601483</v>
+        <v>489254</v>
       </c>
       <c r="R7" t="n">
-        <v>6341198.131531792</v>
+        <v>6341198</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1243,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1372,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73208919</v>
+        <v>96150090</v>
       </c>
       <c r="B8" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,37 +1288,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr om Bastaberget, Sm</t>
+          <t>Bastabergets västsida, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489254.1244601483</v>
+        <v>489275</v>
       </c>
       <c r="R8" t="n">
-        <v>6341198.131531792</v>
+        <v>6341188</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,27 +1346,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På grov asplåga</t>
+          <t>Rikligt i slänten. Fin gammalgranskog med stora aspar, hassel, rönnar mm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,33 +1365,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Staaf, Tobias Ivarsson</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73208955</v>
+        <v>73208917</v>
       </c>
       <c r="B9" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4660</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489249.957817401</v>
+        <v>489226</v>
       </c>
       <c r="R9" t="n">
-        <v>6341264.747223295</v>
+        <v>6341178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,19 +1452,14 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På grov asplåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,15 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96150090</v>
+        <v>73208918</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,41 +1497,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bastabergets västsida, Sm</t>
+          <t>Norr om Bastaberget, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489274.7168507476</v>
+        <v>489254</v>
       </c>
       <c r="R10" t="n">
-        <v>6341188.330690596</v>
+        <v>6341198</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,27 +1551,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt i slänten. Fin gammalgranskog med stora aspar, hassel, rönnar mm.</t>
+          <t>På grov asplåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,19 +1570,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Johan Staaf, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 25236-2026 artfynd.xlsx
+++ b/artfynd/A 25236-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73208936</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73208937</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73208938</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73208955</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73208920</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73208919</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96150090</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73208917</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,8 +1630,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73208918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>